--- a/Project/BL/MDK/McuSTUDIO_F470VET6_analysis.xlsx
+++ b/Project/BL/MDK/McuSTUDIO_F470VET6_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="49">
   <si>
     <t>McuSTUDIO_F470VET6</t>
   </si>
@@ -35,6 +35,9 @@
     <t>oled.o</t>
   </si>
   <si>
+    <t>gd32f4xx_it.o</t>
+  </si>
+  <si>
     <t>systick.o</t>
   </si>
   <si>
@@ -78,9 +81,6 @@
   </si>
   <si>
     <t>ddiv.o</t>
-  </si>
-  <si>
-    <t>gd32f4xx_it.o</t>
   </si>
   <si>
     <t>depilogue.o</t>
@@ -270,9 +270,12 @@
                   <c:v>oled.o</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>gd32f4xx_it.o</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>systick.o</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>system_gd32f4xx.o</c:v>
                 </c:pt>
                 <c:pt idx="38">
@@ -288,25 +291,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="39"/>
                 <c:pt idx="0">
-                  <c:v>62.56300735473633</c:v>
+                  <c:v>42.56247711181641</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>31.28150367736816</c:v>
+                  <c:v>42.56247711181641</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.940736293792725</c:v>
+                  <c:v>13.32155704498291</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.978005170822144</c:v>
+                  <c:v>1.345664262771606</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.1756529659032822</c:v>
+                  <c:v>0.1194991394877434</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.03054834343492985</c:v>
+                  <c:v>0.04676053300499916</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.03054834343492985</c:v>
+                  <c:v>0.02078245952725411</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.02078245952725411</c:v>
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>0</c:v>
@@ -380,16 +386,16 @@
               <c:strCache>
                 <c:ptCount val="39"/>
                 <c:pt idx="0">
+                  <c:v>bl_core.o</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>oled.o</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>printfa.o</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>bl_core.o</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>mf_w.l</c:v>
@@ -419,22 +425,22 @@
                   <c:v>dadd.o</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>gd32f4xx_it.o</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>gd32f4xx_rcu.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>gd32f4xx_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>gd32f4xx_misc.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>dmul.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>ddiv.o</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>gd32f4xx_it.o</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>depilogue.o</c:v>
@@ -506,118 +512,118 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="39"/>
                 <c:pt idx="0">
-                  <c:v>20.3138484954834</c:v>
+                  <c:v>18.6845817565918</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>14.54918003082275</c:v>
+                  <c:v>18.33893203735352</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12.40293312072754</c:v>
+                  <c:v>13.38785839080811</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.95534896850586</c:v>
+                  <c:v>11.450270652771</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.748489856719971</c:v>
+                  <c:v>5.189620971679688</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.033649921417236</c:v>
+                  <c:v>4.089382171630859</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.170836925506592</c:v>
+                  <c:v>2.862567663192749</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.84728217124939</c:v>
+                  <c:v>2.804147720336914</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.502156972885132</c:v>
+                  <c:v>2.258896827697754</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.426661014556885</c:v>
+                  <c:v>2.190740585327148</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.361949920654297</c:v>
+                  <c:v>2.132320642471314</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.200172662734985</c:v>
+                  <c:v>1.986271381378174</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.801121711730957</c:v>
+                  <c:v>1.62601625919342</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.553063035011292</c:v>
+                  <c:v>1.587069749832153</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.466781735420227</c:v>
+                  <c:v>1.402073860168457</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.305004358291626</c:v>
+                  <c:v>1.324180960655212</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.2295081615448</c:v>
+                  <c:v>1.178131580352783</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.197152733802795</c:v>
+                  <c:v>1.109975218772888</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.046160459518433</c:v>
+                  <c:v>1.080765247344971</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.0030198097229</c:v>
+                  <c:v>0.9055060744285584</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.8843830823898315</c:v>
+                  <c:v>0.7984032034873962</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.7657463550567627</c:v>
+                  <c:v>0.6913003325462341</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.5284728407859802</c:v>
+                  <c:v>0.4770945906639099</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.4745470285415649</c:v>
+                  <c:v>0.4284114837646484</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.2588438391685486</c:v>
+                  <c:v>0.2336789816617966</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.2588438391685486</c:v>
+                  <c:v>0.2336789816617966</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.2372735142707825</c:v>
+                  <c:v>0.2142057418823242</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.1941328793764114</c:v>
+                  <c:v>0.1752592325210571</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.1941328793764114</c:v>
+                  <c:v>0.1752592325210571</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.1941328793764114</c:v>
+                  <c:v>0.1752592325210571</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.1941328793764114</c:v>
+                  <c:v>0.1752592325210571</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.1725625544786453</c:v>
+                  <c:v>0.1557859927415848</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.1617773920297623</c:v>
+                  <c:v>0.146049365401268</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.1617773920297623</c:v>
+                  <c:v>0.146049365401268</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.09706643968820572</c:v>
+                  <c:v>0.08762961626052856</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.04314063861966133</c:v>
+                  <c:v>0.03894649818539619</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.04314063861966133</c:v>
+                  <c:v>0.03894649818539619</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.02157031930983067</c:v>
+                  <c:v>0.0194732490926981</c:v>
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>0</c:v>
@@ -1084,7 +1090,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>62.56300735473633</v>
+        <v>42.56247711181641</v>
       </c>
       <c r="C3" s="1">
         <v>8192</v>
@@ -1110,25 +1116,25 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>31.28150367736816</v>
+        <v>42.56247711181641</v>
       </c>
       <c r="C4" s="1">
-        <v>4096</v>
+        <v>8192</v>
       </c>
       <c r="D4" s="1">
-        <v>2217</v>
+        <v>3838</v>
       </c>
       <c r="E4" s="1">
-        <v>2054</v>
+        <v>3762</v>
       </c>
       <c r="F4" s="1">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>4096</v>
+        <v>8192</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1136,16 +1142,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>3.940736293792725</v>
+        <v>13.32155704498291</v>
       </c>
       <c r="C5" s="1">
-        <v>516</v>
+        <v>2564</v>
       </c>
       <c r="D5" s="1">
-        <v>748</v>
+        <v>840</v>
       </c>
       <c r="E5" s="1">
-        <v>746</v>
+        <v>838</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -1154,7 +1160,7 @@
         <v>2</v>
       </c>
       <c r="H5" s="1">
-        <v>514</v>
+        <v>2562</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1162,7 +1168,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>1.978005170822144</v>
+        <v>1.345664262771606</v>
       </c>
       <c r="C6" s="1">
         <v>259</v>
@@ -1188,7 +1194,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.1756529659032822</v>
+        <v>0.1194991394877434</v>
       </c>
       <c r="C7" s="1">
         <v>23</v>
@@ -1214,16 +1220,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.03054834343492985</v>
+        <v>0.04676053300499916</v>
       </c>
       <c r="C8" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D8" s="1">
-        <v>142</v>
+        <v>326</v>
       </c>
       <c r="E8" s="1">
-        <v>142</v>
+        <v>326</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -1232,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1240,24 +1246,50 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.03054834343492985</v>
+        <v>0.02078245952725411</v>
       </c>
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1">
+        <v>142</v>
+      </c>
+      <c r="E9" s="1">
+        <v>142</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.02078245952725411</v>
+      </c>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+      <c r="D10" s="1">
         <v>588</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E10" s="1">
         <v>584</v>
       </c>
-      <c r="F9" s="1">
-        <v>0</v>
-      </c>
-      <c r="G9" s="1">
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
         <v>4</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H10" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1344,51 +1376,51 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>20.3138484954834</v>
+        <v>18.6845817565918</v>
       </c>
       <c r="C3" s="1">
-        <v>3767</v>
+        <v>3838</v>
       </c>
       <c r="D3" s="1">
-        <v>23</v>
+        <v>8192</v>
       </c>
       <c r="E3" s="1">
-        <v>1672</v>
+        <v>3762</v>
       </c>
       <c r="F3" s="1">
-        <v>2072</v>
+        <v>76</v>
       </c>
       <c r="G3" s="1">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>8192</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2">
-        <v>14.54918003082275</v>
+        <v>18.33893203735352</v>
       </c>
       <c r="C4" s="1">
-        <v>2698</v>
+        <v>3767</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1">
-        <v>2698</v>
+        <v>1672</v>
       </c>
       <c r="F4" s="1">
-        <v>0</v>
+        <v>2072</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H4" s="1">
         <v>0</v>
@@ -1399,16 +1431,16 @@
         <v>9</v>
       </c>
       <c r="B5" s="2">
-        <v>12.40293312072754</v>
+        <v>13.38785839080811</v>
       </c>
       <c r="C5" s="1">
-        <v>2300</v>
+        <v>2750</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
       </c>
       <c r="E5" s="1">
-        <v>2300</v>
+        <v>2750</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -1422,36 +1454,36 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2">
-        <v>11.95534896850586</v>
+        <v>11.450270652771</v>
       </c>
       <c r="C6" s="1">
-        <v>2217</v>
+        <v>2352</v>
       </c>
       <c r="D6" s="1">
-        <v>4096</v>
+        <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>2054</v>
+        <v>2352</v>
       </c>
       <c r="F6" s="1">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>4096</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" s="2">
-        <v>5.748489856719971</v>
+        <v>5.189620971679688</v>
       </c>
       <c r="C7" s="1">
         <v>1066</v>
@@ -1477,16 +1509,16 @@
         <v>3</v>
       </c>
       <c r="B8" s="2">
-        <v>4.033649921417236</v>
+        <v>4.089382171630859</v>
       </c>
       <c r="C8" s="1">
-        <v>748</v>
+        <v>840</v>
       </c>
       <c r="D8" s="1">
-        <v>516</v>
+        <v>2564</v>
       </c>
       <c r="E8" s="1">
-        <v>746</v>
+        <v>838</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -1495,15 +1527,15 @@
         <v>2</v>
       </c>
       <c r="H8" s="1">
-        <v>514</v>
+        <v>2562</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>3.170836925506592</v>
+        <v>2.862567663192749</v>
       </c>
       <c r="C9" s="1">
         <v>588</v>
@@ -1526,19 +1558,19 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" s="2">
-        <v>2.84728217124939</v>
+        <v>2.804147720336914</v>
       </c>
       <c r="C10" s="1">
-        <v>528</v>
+        <v>576</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>528</v>
+        <v>576</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -1555,7 +1587,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="2">
-        <v>2.502156972885132</v>
+        <v>2.258896827697754</v>
       </c>
       <c r="C11" s="1">
         <v>464</v>
@@ -1578,10 +1610,10 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" s="2">
-        <v>2.426661014556885</v>
+        <v>2.190740585327148</v>
       </c>
       <c r="C12" s="1">
         <v>450</v>
@@ -1604,10 +1636,10 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13" s="2">
-        <v>2.361949920654297</v>
+        <v>2.132320642471314</v>
       </c>
       <c r="C13" s="1">
         <v>438</v>
@@ -1630,10 +1662,10 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14" s="2">
-        <v>2.200172662734985</v>
+        <v>1.986271381378174</v>
       </c>
       <c r="C14" s="1">
         <v>408</v>
@@ -1656,10 +1688,10 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B15" s="2">
-        <v>1.801121711730957</v>
+        <v>1.62601625919342</v>
       </c>
       <c r="C15" s="1">
         <v>334</v>
@@ -1682,19 +1714,19 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B16" s="2">
-        <v>1.553063035011292</v>
+        <v>1.587069749832153</v>
       </c>
       <c r="C16" s="1">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="D16" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E16" s="1">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -1703,7 +1735,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1711,16 +1743,16 @@
         <v>17</v>
       </c>
       <c r="B17" s="2">
-        <v>1.466781735420227</v>
+        <v>1.402073860168457</v>
       </c>
       <c r="C17" s="1">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -1737,16 +1769,16 @@
         <v>18</v>
       </c>
       <c r="B18" s="2">
-        <v>1.305004358291626</v>
+        <v>1.324180960655212</v>
       </c>
       <c r="C18" s="1">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1763,16 +1795,16 @@
         <v>19</v>
       </c>
       <c r="B19" s="2">
-        <v>1.2295081615448</v>
+        <v>1.178131580352783</v>
       </c>
       <c r="C19" s="1">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -1789,16 +1821,16 @@
         <v>20</v>
       </c>
       <c r="B20" s="2">
-        <v>1.197152733802795</v>
+        <v>1.109975218772888</v>
       </c>
       <c r="C20" s="1">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -1815,16 +1847,16 @@
         <v>21</v>
       </c>
       <c r="B21" s="2">
-        <v>1.046160459518433</v>
+        <v>1.080765247344971</v>
       </c>
       <c r="C21" s="1">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -1841,7 +1873,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2">
-        <v>1.0030198097229</v>
+        <v>0.9055060744285584</v>
       </c>
       <c r="C22" s="1">
         <v>186</v>
@@ -1867,7 +1899,7 @@
         <v>4</v>
       </c>
       <c r="B23" s="2">
-        <v>0.8843830823898315</v>
+        <v>0.7984032034873962</v>
       </c>
       <c r="C23" s="1">
         <v>164</v>
@@ -1890,10 +1922,10 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B24" s="2">
-        <v>0.7657463550567627</v>
+        <v>0.6913003325462341</v>
       </c>
       <c r="C24" s="1">
         <v>142</v>
@@ -1919,7 +1951,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.5284728407859802</v>
+        <v>0.4770945906639099</v>
       </c>
       <c r="C25" s="1">
         <v>98</v>
@@ -1945,7 +1977,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.4745470285415649</v>
+        <v>0.4284114837646484</v>
       </c>
       <c r="C26" s="1">
         <v>88</v>
@@ -1971,7 +2003,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.2588438391685486</v>
+        <v>0.2336789816617966</v>
       </c>
       <c r="C27" s="1">
         <v>48</v>
@@ -1997,7 +2029,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.2588438391685486</v>
+        <v>0.2336789816617966</v>
       </c>
       <c r="C28" s="1">
         <v>48</v>
@@ -2023,7 +2055,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.2372735142707825</v>
+        <v>0.2142057418823242</v>
       </c>
       <c r="C29" s="1">
         <v>44</v>
@@ -2049,7 +2081,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.1941328793764114</v>
+        <v>0.1752592325210571</v>
       </c>
       <c r="C30" s="1">
         <v>36</v>
@@ -2075,7 +2107,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.1941328793764114</v>
+        <v>0.1752592325210571</v>
       </c>
       <c r="C31" s="1">
         <v>36</v>
@@ -2101,7 +2133,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.1941328793764114</v>
+        <v>0.1752592325210571</v>
       </c>
       <c r="C32" s="1">
         <v>36</v>
@@ -2127,7 +2159,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.1941328793764114</v>
+        <v>0.1752592325210571</v>
       </c>
       <c r="C33" s="1">
         <v>36</v>
@@ -2153,7 +2185,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.1725625544786453</v>
+        <v>0.1557859927415848</v>
       </c>
       <c r="C34" s="1">
         <v>32</v>
@@ -2179,7 +2211,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.1617773920297623</v>
+        <v>0.146049365401268</v>
       </c>
       <c r="C35" s="1">
         <v>30</v>
@@ -2205,7 +2237,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.1617773920297623</v>
+        <v>0.146049365401268</v>
       </c>
       <c r="C36" s="1">
         <v>30</v>
@@ -2231,7 +2263,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.09706643968820572</v>
+        <v>0.08762961626052856</v>
       </c>
       <c r="C37" s="1">
         <v>18</v>
@@ -2257,7 +2289,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.04314063861966133</v>
+        <v>0.03894649818539619</v>
       </c>
       <c r="C38" s="1">
         <v>8</v>
@@ -2283,7 +2315,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="2">
-        <v>0.04314063861966133</v>
+        <v>0.03894649818539619</v>
       </c>
       <c r="C39" s="1">
         <v>8</v>
@@ -2309,7 +2341,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="2">
-        <v>0.02157031930983067</v>
+        <v>0.0194732490926981</v>
       </c>
       <c r="C40" s="1">
         <v>4</v>

--- a/Project/BL/MDK/McuSTUDIO_F470VET6_analysis.xlsx
+++ b/Project/BL/MDK/McuSTUDIO_F470VET6_analysis.xlsx
@@ -291,28 +291,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="39"/>
                 <c:pt idx="0">
-                  <c:v>42.56247711181641</c:v>
+                  <c:v>42.57132339477539</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>42.56247711181641</c:v>
+                  <c:v>42.57132339477539</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>13.32155704498291</c:v>
+                  <c:v>13.32432556152344</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.345664262771606</c:v>
+                  <c:v>1.345943927764893</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.1194991394877434</c:v>
+                  <c:v>0.1195239797234535</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.04676053300499916</c:v>
+                  <c:v>0.02598347514867783</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.02078245952725411</c:v>
+                  <c:v>0.02078677900135517</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.02078245952725411</c:v>
+                  <c:v>0.02078677900135517</c:v>
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>0</c:v>
@@ -386,10 +386,10 @@
               <c:strCache>
                 <c:ptCount val="39"/>
                 <c:pt idx="0">
+                  <c:v>oled.o</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>bl_core.o</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>oled.o</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>mc_w.l</c:v>
@@ -512,118 +512,118 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="39"/>
                 <c:pt idx="0">
-                  <c:v>18.6845817565918</c:v>
+                  <c:v>18.49560546875</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>18.33893203735352</c:v>
+                  <c:v>18.05862426757813</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>13.38785839080811</c:v>
+                  <c:v>13.50223445892334</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.450270652771</c:v>
+                  <c:v>11.54809284210205</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.189620971679688</c:v>
+                  <c:v>5.233956813812256</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.089382171630859</c:v>
+                  <c:v>4.124318599700928</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.862567663192749</c:v>
+                  <c:v>2.887023210525513</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.804147720336914</c:v>
+                  <c:v>2.828104257583618</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.258896827697754</c:v>
+                  <c:v>2.278195142745972</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.190740585327148</c:v>
+                  <c:v>2.209456443786621</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.132320642471314</c:v>
+                  <c:v>2.150537729263306</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.986271381378174</c:v>
+                  <c:v>2.003240585327148</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.62601625919342</c:v>
+                  <c:v>1.639907717704773</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.587069749832153</c:v>
+                  <c:v>1.531889796257019</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.402073860168457</c:v>
+                  <c:v>1.414052128791809</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.324180960655212</c:v>
+                  <c:v>1.335493683815002</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.178131580352783</c:v>
+                  <c:v>1.188196539878845</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.109975218772888</c:v>
+                  <c:v>1.119457960128784</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.080765247344971</c:v>
+                  <c:v>1.089998483657837</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.9055060744285584</c:v>
+                  <c:v>0.913241982460022</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.7984032034873962</c:v>
+                  <c:v>0.8052241206169128</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.6913003325462341</c:v>
+                  <c:v>0.6972062587738037</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.4770945906639099</c:v>
+                  <c:v>0.4811705350875855</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.4284114837646484</c:v>
+                  <c:v>0.4320714771747589</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.2336789816617966</c:v>
+                  <c:v>0.2356753498315811</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.2336789816617966</c:v>
+                  <c:v>0.2356753498315811</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.2142057418823242</c:v>
+                  <c:v>0.2160357385873795</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.1752592325210571</c:v>
+                  <c:v>0.1767565160989761</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.1752592325210571</c:v>
+                  <c:v>0.1767565160989761</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.1752592325210571</c:v>
+                  <c:v>0.1767565160989761</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.1752592325210571</c:v>
+                  <c:v>0.1767565160989761</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.1557859927415848</c:v>
+                  <c:v>0.1571169048547745</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.146049365401268</c:v>
+                  <c:v>0.1472970992326737</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.146049365401268</c:v>
+                  <c:v>0.1472970992326737</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.08762961626052856</c:v>
+                  <c:v>0.08837825804948807</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.03894649818539619</c:v>
+                  <c:v>0.03927922621369362</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.03894649818539619</c:v>
+                  <c:v>0.03927922621369362</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.0194732490926981</c:v>
+                  <c:v>0.01963961310684681</c:v>
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>0</c:v>
@@ -1090,7 +1090,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>42.56247711181641</v>
+        <v>42.57132339477539</v>
       </c>
       <c r="C3" s="1">
         <v>8192</v>
@@ -1116,16 +1116,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>42.56247711181641</v>
+        <v>42.57132339477539</v>
       </c>
       <c r="C4" s="1">
         <v>8192</v>
       </c>
       <c r="D4" s="1">
-        <v>3838</v>
+        <v>3678</v>
       </c>
       <c r="E4" s="1">
-        <v>3762</v>
+        <v>3602</v>
       </c>
       <c r="F4" s="1">
         <v>76</v>
@@ -1142,7 +1142,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>13.32155704498291</v>
+        <v>13.32432556152344</v>
       </c>
       <c r="C5" s="1">
         <v>2564</v>
@@ -1168,7 +1168,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>1.345664262771606</v>
+        <v>1.345943927764893</v>
       </c>
       <c r="C6" s="1">
         <v>259</v>
@@ -1194,7 +1194,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.1194991394877434</v>
+        <v>0.1195239797234535</v>
       </c>
       <c r="C7" s="1">
         <v>23</v>
@@ -1220,16 +1220,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.04676053300499916</v>
+        <v>0.02598347514867783</v>
       </c>
       <c r="C8" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D8" s="1">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="E8" s="1">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -1238,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1246,7 +1246,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.02078245952725411</v>
+        <v>0.02078677900135517</v>
       </c>
       <c r="C9" s="1">
         <v>4</v>
@@ -1272,7 +1272,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.02078245952725411</v>
+        <v>0.02078677900135517</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
@@ -1376,54 +1376,54 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>18.6845817565918</v>
+        <v>18.49560546875</v>
       </c>
       <c r="C3" s="1">
-        <v>3838</v>
+        <v>3767</v>
       </c>
       <c r="D3" s="1">
-        <v>8192</v>
+        <v>23</v>
       </c>
       <c r="E3" s="1">
-        <v>3762</v>
+        <v>1672</v>
       </c>
       <c r="F3" s="1">
-        <v>76</v>
+        <v>2072</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H3" s="1">
-        <v>8192</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>18.33893203735352</v>
+        <v>18.05862426757813</v>
       </c>
       <c r="C4" s="1">
-        <v>3767</v>
+        <v>3678</v>
       </c>
       <c r="D4" s="1">
-        <v>23</v>
+        <v>8192</v>
       </c>
       <c r="E4" s="1">
-        <v>1672</v>
+        <v>3602</v>
       </c>
       <c r="F4" s="1">
-        <v>2072</v>
+        <v>76</v>
       </c>
       <c r="G4" s="1">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>8192</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1431,7 +1431,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="2">
-        <v>13.38785839080811</v>
+        <v>13.50223445892334</v>
       </c>
       <c r="C5" s="1">
         <v>2750</v>
@@ -1457,7 +1457,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="2">
-        <v>11.450270652771</v>
+        <v>11.54809284210205</v>
       </c>
       <c r="C6" s="1">
         <v>2352</v>
@@ -1483,7 +1483,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="2">
-        <v>5.189620971679688</v>
+        <v>5.233956813812256</v>
       </c>
       <c r="C7" s="1">
         <v>1066</v>
@@ -1509,7 +1509,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="2">
-        <v>4.089382171630859</v>
+        <v>4.124318599700928</v>
       </c>
       <c r="C8" s="1">
         <v>840</v>
@@ -1535,7 +1535,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>2.862567663192749</v>
+        <v>2.887023210525513</v>
       </c>
       <c r="C9" s="1">
         <v>588</v>
@@ -1561,7 +1561,7 @@
         <v>12</v>
       </c>
       <c r="B10" s="2">
-        <v>2.804147720336914</v>
+        <v>2.828104257583618</v>
       </c>
       <c r="C10" s="1">
         <v>576</v>
@@ -1587,7 +1587,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="2">
-        <v>2.258896827697754</v>
+        <v>2.278195142745972</v>
       </c>
       <c r="C11" s="1">
         <v>464</v>
@@ -1613,7 +1613,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="2">
-        <v>2.190740585327148</v>
+        <v>2.209456443786621</v>
       </c>
       <c r="C12" s="1">
         <v>450</v>
@@ -1639,7 +1639,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="2">
-        <v>2.132320642471314</v>
+        <v>2.150537729263306</v>
       </c>
       <c r="C13" s="1">
         <v>438</v>
@@ -1665,7 +1665,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="2">
-        <v>1.986271381378174</v>
+        <v>2.003240585327148</v>
       </c>
       <c r="C14" s="1">
         <v>408</v>
@@ -1691,7 +1691,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="2">
-        <v>1.62601625919342</v>
+        <v>1.639907717704773</v>
       </c>
       <c r="C15" s="1">
         <v>334</v>
@@ -1717,16 +1717,16 @@
         <v>6</v>
       </c>
       <c r="B16" s="2">
-        <v>1.587069749832153</v>
+        <v>1.531889796257019</v>
       </c>
       <c r="C16" s="1">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="D16" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E16" s="1">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -1735,7 +1735,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1743,7 +1743,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2">
-        <v>1.402073860168457</v>
+        <v>1.414052128791809</v>
       </c>
       <c r="C17" s="1">
         <v>288</v>
@@ -1769,7 +1769,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2">
-        <v>1.324180960655212</v>
+        <v>1.335493683815002</v>
       </c>
       <c r="C18" s="1">
         <v>272</v>
@@ -1795,7 +1795,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="2">
-        <v>1.178131580352783</v>
+        <v>1.188196539878845</v>
       </c>
       <c r="C19" s="1">
         <v>242</v>
@@ -1821,7 +1821,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2">
-        <v>1.109975218772888</v>
+        <v>1.119457960128784</v>
       </c>
       <c r="C20" s="1">
         <v>228</v>
@@ -1847,7 +1847,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2">
-        <v>1.080765247344971</v>
+        <v>1.089998483657837</v>
       </c>
       <c r="C21" s="1">
         <v>222</v>
@@ -1873,7 +1873,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2">
-        <v>0.9055060744285584</v>
+        <v>0.913241982460022</v>
       </c>
       <c r="C22" s="1">
         <v>186</v>
@@ -1899,7 +1899,7 @@
         <v>4</v>
       </c>
       <c r="B23" s="2">
-        <v>0.7984032034873962</v>
+        <v>0.8052241206169128</v>
       </c>
       <c r="C23" s="1">
         <v>164</v>
@@ -1925,7 +1925,7 @@
         <v>7</v>
       </c>
       <c r="B24" s="2">
-        <v>0.6913003325462341</v>
+        <v>0.6972062587738037</v>
       </c>
       <c r="C24" s="1">
         <v>142</v>
@@ -1951,7 +1951,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.4770945906639099</v>
+        <v>0.4811705350875855</v>
       </c>
       <c r="C25" s="1">
         <v>98</v>
@@ -1977,7 +1977,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.4284114837646484</v>
+        <v>0.4320714771747589</v>
       </c>
       <c r="C26" s="1">
         <v>88</v>
@@ -2003,7 +2003,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.2336789816617966</v>
+        <v>0.2356753498315811</v>
       </c>
       <c r="C27" s="1">
         <v>48</v>
@@ -2029,7 +2029,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.2336789816617966</v>
+        <v>0.2356753498315811</v>
       </c>
       <c r="C28" s="1">
         <v>48</v>
@@ -2055,7 +2055,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.2142057418823242</v>
+        <v>0.2160357385873795</v>
       </c>
       <c r="C29" s="1">
         <v>44</v>
@@ -2081,7 +2081,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.1752592325210571</v>
+        <v>0.1767565160989761</v>
       </c>
       <c r="C30" s="1">
         <v>36</v>
@@ -2107,7 +2107,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.1752592325210571</v>
+        <v>0.1767565160989761</v>
       </c>
       <c r="C31" s="1">
         <v>36</v>
@@ -2133,7 +2133,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.1752592325210571</v>
+        <v>0.1767565160989761</v>
       </c>
       <c r="C32" s="1">
         <v>36</v>
@@ -2159,7 +2159,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.1752592325210571</v>
+        <v>0.1767565160989761</v>
       </c>
       <c r="C33" s="1">
         <v>36</v>
@@ -2185,7 +2185,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.1557859927415848</v>
+        <v>0.1571169048547745</v>
       </c>
       <c r="C34" s="1">
         <v>32</v>
@@ -2211,7 +2211,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.146049365401268</v>
+        <v>0.1472970992326737</v>
       </c>
       <c r="C35" s="1">
         <v>30</v>
@@ -2237,7 +2237,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.146049365401268</v>
+        <v>0.1472970992326737</v>
       </c>
       <c r="C36" s="1">
         <v>30</v>
@@ -2263,7 +2263,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.08762961626052856</v>
+        <v>0.08837825804948807</v>
       </c>
       <c r="C37" s="1">
         <v>18</v>
@@ -2289,7 +2289,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.03894649818539619</v>
+        <v>0.03927922621369362</v>
       </c>
       <c r="C38" s="1">
         <v>8</v>
@@ -2315,7 +2315,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="2">
-        <v>0.03894649818539619</v>
+        <v>0.03927922621369362</v>
       </c>
       <c r="C39" s="1">
         <v>8</v>
@@ -2341,7 +2341,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="2">
-        <v>0.0194732490926981</v>
+        <v>0.01963961310684681</v>
       </c>
       <c r="C40" s="1">
         <v>4</v>

--- a/Project/BL/MDK/McuSTUDIO_F470VET6_analysis.xlsx
+++ b/Project/BL/MDK/McuSTUDIO_F470VET6_analysis.xlsx
@@ -291,28 +291,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="39"/>
                 <c:pt idx="0">
-                  <c:v>42.57132339477539</c:v>
+                  <c:v>54.06903839111328</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>42.57132339477539</c:v>
+                  <c:v>27.06092071533203</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>13.32432556152344</c:v>
+                  <c:v>16.92297554016113</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.345943927764893</c:v>
+                  <c:v>1.709458112716675</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.1195239797234535</c:v>
+                  <c:v>0.1518051624298096</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.02598347514867783</c:v>
+                  <c:v>0.0330011211335659</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.02078677900135517</c:v>
+                  <c:v>0.02640089765191078</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.02078677900135517</c:v>
+                  <c:v>0.02640089765191078</c:v>
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>0</c:v>
@@ -386,10 +386,10 @@
               <c:strCache>
                 <c:ptCount val="39"/>
                 <c:pt idx="0">
+                  <c:v>bl_core.o</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>oled.o</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>bl_core.o</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>mc_w.l</c:v>
@@ -410,10 +410,10 @@
                   <c:v>gd32f4xx_usart.o</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>gd32f4xx_dma.o</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>startup_gd32f450_470.o</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>gd32f4xx_dma.o</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>gd32f4xx_i2c.o</c:v>
@@ -512,118 +512,118 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="39"/>
                 <c:pt idx="0">
-                  <c:v>18.49560546875</c:v>
+                  <c:v>19.03421592712402</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>18.05862426757813</c:v>
+                  <c:v>18.2819709777832</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>13.50223445892334</c:v>
+                  <c:v>13.34627532958984</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.54809284210205</c:v>
+                  <c:v>11.41470527648926</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.233956813812256</c:v>
+                  <c:v>5.173501491546631</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.124318599700928</c:v>
+                  <c:v>4.076680183410645</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.887023210525513</c:v>
+                  <c:v>2.853676319122315</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.828104257583618</c:v>
+                  <c:v>2.678961515426636</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.278195142745972</c:v>
+                  <c:v>2.27129340171814</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.209456443786621</c:v>
+                  <c:v>2.251880645751953</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.150537729263306</c:v>
+                  <c:v>2.125697612762451</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.003240585327148</c:v>
+                  <c:v>1.980101943016052</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.639907717704773</c:v>
+                  <c:v>1.620965838432312</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.531889796257019</c:v>
+                  <c:v>1.514195561408997</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.414052128791809</c:v>
+                  <c:v>1.397719025611877</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.335493683815002</c:v>
+                  <c:v>1.320068001747131</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.188196539878845</c:v>
+                  <c:v>1.174472212791443</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.119457960128784</c:v>
+                  <c:v>1.10652756690979</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.089998483657837</c:v>
+                  <c:v>1.07740843296051</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.913241982460022</c:v>
+                  <c:v>0.902693510055542</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.8052241206169128</c:v>
+                  <c:v>0.7959232926368713</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.6972062587738037</c:v>
+                  <c:v>0.6891531348228455</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.4811705350875855</c:v>
+                  <c:v>0.4756127297878265</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.4320714771747589</c:v>
+                  <c:v>0.4270808100700378</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.2356753498315811</c:v>
+                  <c:v>0.2329531610012054</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.2356753498315811</c:v>
+                  <c:v>0.2329531610012054</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.2160357385873795</c:v>
+                  <c:v>0.2135404050350189</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.1767565160989761</c:v>
+                  <c:v>0.1747148782014847</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.1767565160989761</c:v>
+                  <c:v>0.1747148782014847</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.1767565160989761</c:v>
+                  <c:v>0.1747148782014847</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.1767565160989761</c:v>
+                  <c:v>0.1747148782014847</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.1571169048547745</c:v>
+                  <c:v>0.155302107334137</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.1472970992326737</c:v>
+                  <c:v>0.1455957293510437</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.1472970992326737</c:v>
+                  <c:v>0.1455957293510437</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.08837825804948807</c:v>
+                  <c:v>0.08735743910074234</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.03927922621369362</c:v>
+                  <c:v>0.03882552683353424</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.03927922621369362</c:v>
+                  <c:v>0.03882552683353424</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.01963961310684681</c:v>
+                  <c:v>0.01941276341676712</c:v>
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>0</c:v>
@@ -1090,7 +1090,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>42.57132339477539</v>
+        <v>54.06903839111328</v>
       </c>
       <c r="C3" s="1">
         <v>8192</v>
@@ -1116,25 +1116,25 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>42.57132339477539</v>
+        <v>27.06092071533203</v>
       </c>
       <c r="C4" s="1">
-        <v>8192</v>
+        <v>4100</v>
       </c>
       <c r="D4" s="1">
-        <v>3678</v>
+        <v>3922</v>
       </c>
       <c r="E4" s="1">
-        <v>3602</v>
+        <v>3802</v>
       </c>
       <c r="F4" s="1">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>8192</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1142,7 +1142,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>13.32432556152344</v>
+        <v>16.92297554016113</v>
       </c>
       <c r="C5" s="1">
         <v>2564</v>
@@ -1168,7 +1168,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>1.345943927764893</v>
+        <v>1.709458112716675</v>
       </c>
       <c r="C6" s="1">
         <v>259</v>
@@ -1194,7 +1194,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.1195239797234535</v>
+        <v>0.1518051624298096</v>
       </c>
       <c r="C7" s="1">
         <v>23</v>
@@ -1220,7 +1220,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.02598347514867783</v>
+        <v>0.0330011211335659</v>
       </c>
       <c r="C8" s="1">
         <v>5</v>
@@ -1246,7 +1246,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.02078677900135517</v>
+        <v>0.02640089765191078</v>
       </c>
       <c r="C9" s="1">
         <v>4</v>
@@ -1272,7 +1272,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.02078677900135517</v>
+        <v>0.02640089765191078</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
@@ -1376,54 +1376,54 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>18.49560546875</v>
+        <v>19.03421592712402</v>
       </c>
       <c r="C3" s="1">
-        <v>3767</v>
+        <v>3922</v>
       </c>
       <c r="D3" s="1">
-        <v>23</v>
+        <v>4100</v>
       </c>
       <c r="E3" s="1">
-        <v>1672</v>
+        <v>3802</v>
       </c>
       <c r="F3" s="1">
-        <v>2072</v>
+        <v>120</v>
       </c>
       <c r="G3" s="1">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2">
-        <v>18.05862426757813</v>
+        <v>18.2819709777832</v>
       </c>
       <c r="C4" s="1">
-        <v>3678</v>
+        <v>3767</v>
       </c>
       <c r="D4" s="1">
-        <v>8192</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1">
-        <v>3602</v>
+        <v>1672</v>
       </c>
       <c r="F4" s="1">
-        <v>76</v>
+        <v>2072</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H4" s="1">
-        <v>8192</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1431,7 +1431,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="2">
-        <v>13.50223445892334</v>
+        <v>13.34627532958984</v>
       </c>
       <c r="C5" s="1">
         <v>2750</v>
@@ -1457,7 +1457,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="2">
-        <v>11.54809284210205</v>
+        <v>11.41470527648926</v>
       </c>
       <c r="C6" s="1">
         <v>2352</v>
@@ -1483,7 +1483,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="2">
-        <v>5.233956813812256</v>
+        <v>5.173501491546631</v>
       </c>
       <c r="C7" s="1">
         <v>1066</v>
@@ -1509,7 +1509,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="2">
-        <v>4.124318599700928</v>
+        <v>4.076680183410645</v>
       </c>
       <c r="C8" s="1">
         <v>840</v>
@@ -1535,7 +1535,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>2.887023210525513</v>
+        <v>2.853676319122315</v>
       </c>
       <c r="C9" s="1">
         <v>588</v>
@@ -1561,16 +1561,16 @@
         <v>12</v>
       </c>
       <c r="B10" s="2">
-        <v>2.828104257583618</v>
+        <v>2.678961515426636</v>
       </c>
       <c r="C10" s="1">
-        <v>576</v>
+        <v>552</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>576</v>
+        <v>552</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -1584,54 +1584,54 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B11" s="2">
-        <v>2.278195142745972</v>
+        <v>2.27129340171814</v>
       </c>
       <c r="C11" s="1">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="D11" s="1">
-        <v>8192</v>
+        <v>0</v>
       </c>
       <c r="E11" s="1">
-        <v>36</v>
+        <v>468</v>
       </c>
       <c r="F11" s="1">
-        <v>428</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>8192</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B12" s="2">
-        <v>2.209456443786621</v>
+        <v>2.251880645751953</v>
       </c>
       <c r="C12" s="1">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="D12" s="1">
-        <v>0</v>
+        <v>8192</v>
       </c>
       <c r="E12" s="1">
-        <v>450</v>
+        <v>36</v>
       </c>
       <c r="F12" s="1">
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>8192</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1639,7 +1639,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="2">
-        <v>2.150537729263306</v>
+        <v>2.125697612762451</v>
       </c>
       <c r="C13" s="1">
         <v>438</v>
@@ -1665,7 +1665,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="2">
-        <v>2.003240585327148</v>
+        <v>1.980101943016052</v>
       </c>
       <c r="C14" s="1">
         <v>408</v>
@@ -1691,7 +1691,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="2">
-        <v>1.639907717704773</v>
+        <v>1.620965838432312</v>
       </c>
       <c r="C15" s="1">
         <v>334</v>
@@ -1717,7 +1717,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="2">
-        <v>1.531889796257019</v>
+        <v>1.514195561408997</v>
       </c>
       <c r="C16" s="1">
         <v>312</v>
@@ -1743,7 +1743,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2">
-        <v>1.414052128791809</v>
+        <v>1.397719025611877</v>
       </c>
       <c r="C17" s="1">
         <v>288</v>
@@ -1769,7 +1769,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2">
-        <v>1.335493683815002</v>
+        <v>1.320068001747131</v>
       </c>
       <c r="C18" s="1">
         <v>272</v>
@@ -1795,7 +1795,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="2">
-        <v>1.188196539878845</v>
+        <v>1.174472212791443</v>
       </c>
       <c r="C19" s="1">
         <v>242</v>
@@ -1821,7 +1821,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2">
-        <v>1.119457960128784</v>
+        <v>1.10652756690979</v>
       </c>
       <c r="C20" s="1">
         <v>228</v>
@@ -1847,7 +1847,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2">
-        <v>1.089998483657837</v>
+        <v>1.07740843296051</v>
       </c>
       <c r="C21" s="1">
         <v>222</v>
@@ -1873,7 +1873,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2">
-        <v>0.913241982460022</v>
+        <v>0.902693510055542</v>
       </c>
       <c r="C22" s="1">
         <v>186</v>
@@ -1899,7 +1899,7 @@
         <v>4</v>
       </c>
       <c r="B23" s="2">
-        <v>0.8052241206169128</v>
+        <v>0.7959232926368713</v>
       </c>
       <c r="C23" s="1">
         <v>164</v>
@@ -1925,7 +1925,7 @@
         <v>7</v>
       </c>
       <c r="B24" s="2">
-        <v>0.6972062587738037</v>
+        <v>0.6891531348228455</v>
       </c>
       <c r="C24" s="1">
         <v>142</v>
@@ -1951,7 +1951,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.4811705350875855</v>
+        <v>0.4756127297878265</v>
       </c>
       <c r="C25" s="1">
         <v>98</v>
@@ -1977,7 +1977,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.4320714771747589</v>
+        <v>0.4270808100700378</v>
       </c>
       <c r="C26" s="1">
         <v>88</v>
@@ -2003,7 +2003,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.2356753498315811</v>
+        <v>0.2329531610012054</v>
       </c>
       <c r="C27" s="1">
         <v>48</v>
@@ -2029,7 +2029,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.2356753498315811</v>
+        <v>0.2329531610012054</v>
       </c>
       <c r="C28" s="1">
         <v>48</v>
@@ -2055,7 +2055,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.2160357385873795</v>
+        <v>0.2135404050350189</v>
       </c>
       <c r="C29" s="1">
         <v>44</v>
@@ -2081,7 +2081,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.1767565160989761</v>
+        <v>0.1747148782014847</v>
       </c>
       <c r="C30" s="1">
         <v>36</v>
@@ -2107,7 +2107,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.1767565160989761</v>
+        <v>0.1747148782014847</v>
       </c>
       <c r="C31" s="1">
         <v>36</v>
@@ -2133,7 +2133,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.1767565160989761</v>
+        <v>0.1747148782014847</v>
       </c>
       <c r="C32" s="1">
         <v>36</v>
@@ -2159,7 +2159,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.1767565160989761</v>
+        <v>0.1747148782014847</v>
       </c>
       <c r="C33" s="1">
         <v>36</v>
@@ -2185,7 +2185,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.1571169048547745</v>
+        <v>0.155302107334137</v>
       </c>
       <c r="C34" s="1">
         <v>32</v>
@@ -2211,7 +2211,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.1472970992326737</v>
+        <v>0.1455957293510437</v>
       </c>
       <c r="C35" s="1">
         <v>30</v>
@@ -2237,7 +2237,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.1472970992326737</v>
+        <v>0.1455957293510437</v>
       </c>
       <c r="C36" s="1">
         <v>30</v>
@@ -2263,7 +2263,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.08837825804948807</v>
+        <v>0.08735743910074234</v>
       </c>
       <c r="C37" s="1">
         <v>18</v>
@@ -2289,7 +2289,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.03927922621369362</v>
+        <v>0.03882552683353424</v>
       </c>
       <c r="C38" s="1">
         <v>8</v>
@@ -2315,7 +2315,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="2">
-        <v>0.03927922621369362</v>
+        <v>0.03882552683353424</v>
       </c>
       <c r="C39" s="1">
         <v>8</v>
@@ -2341,7 +2341,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="2">
-        <v>0.01963961310684681</v>
+        <v>0.01941276341676712</v>
       </c>
       <c r="C40" s="1">
         <v>4</v>

--- a/Project/BL/MDK/McuSTUDIO_F470VET6_analysis.xlsx
+++ b/Project/BL/MDK/McuSTUDIO_F470VET6_analysis.xlsx
@@ -512,118 +512,118 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="39"/>
                 <c:pt idx="0">
-                  <c:v>19.03421592712402</c:v>
+                  <c:v>19.61766242980957</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>18.2819709777832</c:v>
+                  <c:v>18.13935661315918</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>13.34627532958984</c:v>
+                  <c:v>13.24216270446777</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.41470527648926</c:v>
+                  <c:v>11.32566070556641</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.173501491546631</c:v>
+                  <c:v>5.133143901824951</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.076680183410645</c:v>
+                  <c:v>4.044878959655762</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.853676319122315</c:v>
+                  <c:v>2.831415176391602</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.678961515426636</c:v>
+                  <c:v>2.70621657371521</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.27129340171814</c:v>
+                  <c:v>2.253575325012207</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.251880645751953</c:v>
+                  <c:v>2.23431396484375</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.125697612762451</c:v>
+                  <c:v>2.109115362167358</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.980101943016052</c:v>
+                  <c:v>1.964655518531799</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.620965838432312</c:v>
+                  <c:v>1.608320951461792</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.514195561408997</c:v>
+                  <c:v>1.502383589744568</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.397719025611877</c:v>
+                  <c:v>1.386815667152405</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.320068001747131</c:v>
+                  <c:v>1.309770345687866</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.174472212791443</c:v>
+                  <c:v>1.165310382843018</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.10652756690979</c:v>
+                  <c:v>1.097895741462708</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.07740843296051</c:v>
+                  <c:v>1.069003701210022</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.902693510055542</c:v>
+                  <c:v>0.8956517577171326</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.7959232926368713</c:v>
+                  <c:v>0.7897144556045532</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.6891531348228455</c:v>
+                  <c:v>0.6837771534919739</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.4756127297878265</c:v>
+                  <c:v>0.4719025492668152</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.4270808100700378</c:v>
+                  <c:v>0.4237492084503174</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.2329531610012054</c:v>
+                  <c:v>0.2311359345912933</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.2329531610012054</c:v>
+                  <c:v>0.2311359345912933</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.2135404050350189</c:v>
+                  <c:v>0.2118746042251587</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.1747148782014847</c:v>
+                  <c:v>0.1733519583940506</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.1747148782014847</c:v>
+                  <c:v>0.1733519583940506</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.1747148782014847</c:v>
+                  <c:v>0.1733519583940506</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.1747148782014847</c:v>
+                  <c:v>0.1733519583940506</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.155302107334137</c:v>
+                  <c:v>0.154090628027916</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.1455957293510437</c:v>
+                  <c:v>0.1444599628448486</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.1455957293510437</c:v>
+                  <c:v>0.1444599628448486</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.08735743910074234</c:v>
+                  <c:v>0.0866759791970253</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.03882552683353424</c:v>
+                  <c:v>0.03852265700697899</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.03882552683353424</c:v>
+                  <c:v>0.03852265700697899</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.01941276341676712</c:v>
+                  <c:v>0.01926132850348949</c:v>
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>0</c:v>
@@ -1122,10 +1122,10 @@
         <v>4100</v>
       </c>
       <c r="D4" s="1">
-        <v>3922</v>
+        <v>4074</v>
       </c>
       <c r="E4" s="1">
-        <v>3802</v>
+        <v>3954</v>
       </c>
       <c r="F4" s="1">
         <v>120</v>
@@ -1379,16 +1379,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>19.03421592712402</v>
+        <v>19.61766242980957</v>
       </c>
       <c r="C3" s="1">
-        <v>3922</v>
+        <v>4074</v>
       </c>
       <c r="D3" s="1">
         <v>4100</v>
       </c>
       <c r="E3" s="1">
-        <v>3802</v>
+        <v>3954</v>
       </c>
       <c r="F3" s="1">
         <v>120</v>
@@ -1405,7 +1405,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="2">
-        <v>18.2819709777832</v>
+        <v>18.13935661315918</v>
       </c>
       <c r="C4" s="1">
         <v>3767</v>
@@ -1431,7 +1431,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="2">
-        <v>13.34627532958984</v>
+        <v>13.24216270446777</v>
       </c>
       <c r="C5" s="1">
         <v>2750</v>
@@ -1457,7 +1457,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="2">
-        <v>11.41470527648926</v>
+        <v>11.32566070556641</v>
       </c>
       <c r="C6" s="1">
         <v>2352</v>
@@ -1483,7 +1483,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="2">
-        <v>5.173501491546631</v>
+        <v>5.133143901824951</v>
       </c>
       <c r="C7" s="1">
         <v>1066</v>
@@ -1509,7 +1509,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="2">
-        <v>4.076680183410645</v>
+        <v>4.044878959655762</v>
       </c>
       <c r="C8" s="1">
         <v>840</v>
@@ -1535,7 +1535,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>2.853676319122315</v>
+        <v>2.831415176391602</v>
       </c>
       <c r="C9" s="1">
         <v>588</v>
@@ -1561,16 +1561,16 @@
         <v>12</v>
       </c>
       <c r="B10" s="2">
-        <v>2.678961515426636</v>
+        <v>2.70621657371521</v>
       </c>
       <c r="C10" s="1">
-        <v>552</v>
+        <v>562</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>552</v>
+        <v>562</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>13</v>
       </c>
       <c r="B11" s="2">
-        <v>2.27129340171814</v>
+        <v>2.253575325012207</v>
       </c>
       <c r="C11" s="1">
         <v>468</v>
@@ -1613,7 +1613,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="2">
-        <v>2.251880645751953</v>
+        <v>2.23431396484375</v>
       </c>
       <c r="C12" s="1">
         <v>464</v>
@@ -1639,7 +1639,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="2">
-        <v>2.125697612762451</v>
+        <v>2.109115362167358</v>
       </c>
       <c r="C13" s="1">
         <v>438</v>
@@ -1665,7 +1665,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="2">
-        <v>1.980101943016052</v>
+        <v>1.964655518531799</v>
       </c>
       <c r="C14" s="1">
         <v>408</v>
@@ -1691,7 +1691,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="2">
-        <v>1.620965838432312</v>
+        <v>1.608320951461792</v>
       </c>
       <c r="C15" s="1">
         <v>334</v>
@@ -1717,7 +1717,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="2">
-        <v>1.514195561408997</v>
+        <v>1.502383589744568</v>
       </c>
       <c r="C16" s="1">
         <v>312</v>
@@ -1743,7 +1743,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2">
-        <v>1.397719025611877</v>
+        <v>1.386815667152405</v>
       </c>
       <c r="C17" s="1">
         <v>288</v>
@@ -1769,7 +1769,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2">
-        <v>1.320068001747131</v>
+        <v>1.309770345687866</v>
       </c>
       <c r="C18" s="1">
         <v>272</v>
@@ -1795,7 +1795,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="2">
-        <v>1.174472212791443</v>
+        <v>1.165310382843018</v>
       </c>
       <c r="C19" s="1">
         <v>242</v>
@@ -1821,7 +1821,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2">
-        <v>1.10652756690979</v>
+        <v>1.097895741462708</v>
       </c>
       <c r="C20" s="1">
         <v>228</v>
@@ -1847,7 +1847,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2">
-        <v>1.07740843296051</v>
+        <v>1.069003701210022</v>
       </c>
       <c r="C21" s="1">
         <v>222</v>
@@ -1873,7 +1873,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2">
-        <v>0.902693510055542</v>
+        <v>0.8956517577171326</v>
       </c>
       <c r="C22" s="1">
         <v>186</v>
@@ -1899,7 +1899,7 @@
         <v>4</v>
       </c>
       <c r="B23" s="2">
-        <v>0.7959232926368713</v>
+        <v>0.7897144556045532</v>
       </c>
       <c r="C23" s="1">
         <v>164</v>
@@ -1925,7 +1925,7 @@
         <v>7</v>
       </c>
       <c r="B24" s="2">
-        <v>0.6891531348228455</v>
+        <v>0.6837771534919739</v>
       </c>
       <c r="C24" s="1">
         <v>142</v>
@@ -1951,7 +1951,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.4756127297878265</v>
+        <v>0.4719025492668152</v>
       </c>
       <c r="C25" s="1">
         <v>98</v>
@@ -1977,7 +1977,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.4270808100700378</v>
+        <v>0.4237492084503174</v>
       </c>
       <c r="C26" s="1">
         <v>88</v>
@@ -2003,7 +2003,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.2329531610012054</v>
+        <v>0.2311359345912933</v>
       </c>
       <c r="C27" s="1">
         <v>48</v>
@@ -2029,7 +2029,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.2329531610012054</v>
+        <v>0.2311359345912933</v>
       </c>
       <c r="C28" s="1">
         <v>48</v>
@@ -2055,7 +2055,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.2135404050350189</v>
+        <v>0.2118746042251587</v>
       </c>
       <c r="C29" s="1">
         <v>44</v>
@@ -2081,7 +2081,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.1747148782014847</v>
+        <v>0.1733519583940506</v>
       </c>
       <c r="C30" s="1">
         <v>36</v>
@@ -2107,7 +2107,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.1747148782014847</v>
+        <v>0.1733519583940506</v>
       </c>
       <c r="C31" s="1">
         <v>36</v>
@@ -2133,7 +2133,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.1747148782014847</v>
+        <v>0.1733519583940506</v>
       </c>
       <c r="C32" s="1">
         <v>36</v>
@@ -2159,7 +2159,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.1747148782014847</v>
+        <v>0.1733519583940506</v>
       </c>
       <c r="C33" s="1">
         <v>36</v>
@@ -2185,7 +2185,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.155302107334137</v>
+        <v>0.154090628027916</v>
       </c>
       <c r="C34" s="1">
         <v>32</v>
@@ -2211,7 +2211,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.1455957293510437</v>
+        <v>0.1444599628448486</v>
       </c>
       <c r="C35" s="1">
         <v>30</v>
@@ -2237,7 +2237,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.1455957293510437</v>
+        <v>0.1444599628448486</v>
       </c>
       <c r="C36" s="1">
         <v>30</v>
@@ -2263,7 +2263,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.08735743910074234</v>
+        <v>0.0866759791970253</v>
       </c>
       <c r="C37" s="1">
         <v>18</v>
@@ -2289,7 +2289,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.03882552683353424</v>
+        <v>0.03852265700697899</v>
       </c>
       <c r="C38" s="1">
         <v>8</v>
@@ -2315,7 +2315,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="2">
-        <v>0.03882552683353424</v>
+        <v>0.03852265700697899</v>
       </c>
       <c r="C39" s="1">
         <v>8</v>
@@ -2341,7 +2341,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="2">
-        <v>0.01941276341676712</v>
+        <v>0.01926132850348949</v>
       </c>
       <c r="C40" s="1">
         <v>4</v>
